--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -1,45 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NoguchiTakuya\Documents\Claude\projects\テンプレート作成\03_設計\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8B1AD5-631D-459D-BF28-7F489CC436FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="6570" yWindow="-11835" windowWidth="17280" windowHeight="10680" activeTab="3" xr2:uid="{900B833C-72D3-4F3F-95D9-ED43B39E1931}"/>
+    <workbookView xWindow="6570" yWindow="-11835" windowWidth="17280" windowHeight="10680" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="取引先" sheetId="1" r:id="rId1"/>
-    <sheet name="取引先責任者" sheetId="2" r:id="rId2"/>
-    <sheet name="商談" sheetId="3" r:id="rId3"/>
-    <sheet name="リード" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="取引先" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="取引先責任者" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="164">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -264,6 +242,18 @@
   </si>
   <si>
     <t>カスタム項目、活動履歴から自動更新</t>
+  </si>
+  <si>
+    <t>Test__c</t>
+  </si>
+  <si>
+    <t>テスト項目</t>
+  </si>
+  <si>
+    <t>テスト項目（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、Issue #1 の手順練習用</t>
   </si>
   <si>
     <t>項目定義書　－ 取引先責任者オブジェクト（Contact）</t>
@@ -524,49 +514,49 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="3"/>
+      <scheme val="minor"/>
       <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
+    </font>
+    <font>
       <charset val="128"/>
+      <color theme="1"/>
+      <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="3"/>
+      <scheme val="minor"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFC00000"/>
+      <family val="3"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -643,6 +633,19 @@
       <left style="thin">
         <color rgb="FFD2D2D2"/>
       </left>
+      <right style="thin">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD2D2D2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD2D2D2"/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FFD2D2D2"/>
@@ -667,110 +670,93 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD2D2D2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD2D2D2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD2D2D2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1101,9 +1087,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858D6FC1-04B4-46E2-8A1F-4C11D190D841}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -1114,7 +1100,7 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1113,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1138,7 +1124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1167,7 +1153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -1183,337 +1169,361 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>255</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>40</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19" t="s">
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>40</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>255</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="F13" s="13"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="9" t="s">
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>32000</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="20" t="s">
+      <c r="F15" s="13"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="20" t="s">
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="25" t="s">
+      <c r="H16" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="21" t="s">
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="22" t="s">
+      <c r="E17" s="17"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="17">
+        <v>255</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1583F6D6-C25C-4EB8-9E2B-454A26C07366}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -1524,9 +1534,9 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1537,7 +1547,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1577,12 +1587,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -1593,258 +1603,257 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="10">
         <v>80</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10" t="s">
+      <c r="F6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E7" s="7">
+        <v>40</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="10">
+        <v>128</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7">
         <v>80</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="10">
+        <v>80</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="7">
+        <v>40</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="10">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="9">
-        <v>40</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="12">
-        <v>128</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="9">
-        <v>80</v>
-      </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="12">
-        <v>80</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="9">
-        <v>40</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="12">
-        <v>40</v>
-      </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="14"/>
+      <c r="I14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB16BB33-C7E1-4DB9-B3F1-856C59E6577F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -1855,9 +1864,9 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1868,7 +1877,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1879,7 +1888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1908,12 +1917,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -1924,289 +1933,288 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>120</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="I5" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="26" t="s">
+      <c r="C6" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="I7" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="26" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="B10" s="10" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="I10" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>32000</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="14">
         <v>255</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="25" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="21" t="s">
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>137</v>
+      <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE090E5C-8ADA-443C-821A-ABCAB7449EBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -2217,9 +2225,9 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2230,7 +2238,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2241,7 +2249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2270,12 +2278,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2286,300 +2294,299 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>80</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>40</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>255</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>128</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="F8" s="11"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="7">
         <v>80</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>40</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>32000</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="9" t="s">
+      <c r="F14" s="11"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>159</v>
+      <c r="I16" s="26" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -11,13 +11,14 @@
     <sheet sheetId="2" name="取引先責任者" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="ポイント履歴" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="207">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -334,6 +335,63 @@
     <t>取引先責任者オーナー</t>
   </si>
   <si>
+    <t>CardNumber__c</t>
+  </si>
+  <si>
+    <t>ポイントカード番号</t>
+  </si>
+  <si>
+    <t>ポイントカード番号（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、一意・外部ID。バーコードで読み取る番号</t>
+  </si>
+  <si>
+    <t>PointEarned__c</t>
+  </si>
+  <si>
+    <t>付与ポイント合計</t>
+  </si>
+  <si>
+    <t>付与ポイント合計（カスタム）</t>
+  </si>
+  <si>
+    <t>積み上げ集計</t>
+  </si>
+  <si>
+    <t>自動</t>
+  </si>
+  <si>
+    <t>カスタム項目、ポイント履歴（区分＝付与）のポイント数の合計</t>
+  </si>
+  <si>
+    <t>PointUsed__c</t>
+  </si>
+  <si>
+    <t>利用ポイント合計</t>
+  </si>
+  <si>
+    <t>利用ポイント合計（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、ポイント履歴（区分＝利用）のポイント数の合計</t>
+  </si>
+  <si>
+    <t>PointBalance__c</t>
+  </si>
+  <si>
+    <t>ポイント残高</t>
+  </si>
+  <si>
+    <t>ポイント残高（カスタム）</t>
+  </si>
+  <si>
+    <t>数式（数値）</t>
+  </si>
+  <si>
+    <t>カスタム項目、付与ポイント合計－利用ポイント合計</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -394,9 +452,6 @@
     <t>パーセント</t>
   </si>
   <si>
-    <t>自動</t>
-  </si>
-  <si>
     <t>フェーズに連動して自動設定</t>
   </si>
   <si>
@@ -509,6 +564,81 @@
   </si>
   <si>
     <t>商談化時に自動でTrue</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ポイント履歴オブジェクト（PointHistory__c）</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>ポイント履歴ID</t>
+  </si>
+  <si>
+    <t>ポイント履歴番号</t>
+  </si>
+  <si>
+    <t>PH-00000形式</t>
+  </si>
+  <si>
+    <t>Contact__c</t>
+  </si>
+  <si>
+    <t>お客様</t>
+  </si>
+  <si>
+    <t>主従関係（Contact）</t>
+  </si>
+  <si>
+    <t>取引先責任者への主従関係</t>
+  </si>
+  <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>店舗</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ</t>
+  </si>
+  <si>
+    <t>グローバル値セット「店舗」を利用</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>付与/利用</t>
+  </si>
+  <si>
+    <t>初期値：付与</t>
+  </si>
+  <si>
+    <t>Points__c</t>
+  </si>
+  <si>
+    <t>ポイント数</t>
+  </si>
+  <si>
+    <t>正の整数で入力</t>
+  </si>
+  <si>
+    <t>PurchaseAmount__c</t>
+  </si>
+  <si>
+    <t>購入金額</t>
+  </si>
+  <si>
+    <t>付与時の購入金額</t>
+  </si>
+  <si>
+    <t>TransactionDate__c</t>
+  </si>
+  <si>
+    <t>初期値：今日</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1841,6 +1971,100 @@
         <v>9</v>
       </c>
       <c r="I14" s="23"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="21">
+        <v>20</v>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>123</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1866,7 +2090,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1877,7 +2101,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1919,10 +2143,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -1947,10 +2171,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -1966,7 +2190,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1994,13 +2218,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2010,24 +2234,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2044,13 +2268,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2065,36 +2289,36 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2102,7 +2326,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2117,7 +2341,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2137,7 +2361,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2155,13 +2379,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2180,13 +2404,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2194,13 +2418,13 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2227,7 +2451,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2280,10 +2504,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2353,13 +2577,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2447,13 +2671,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2463,7 +2687,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -2472,13 +2696,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -2486,7 +2710,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -2495,13 +2719,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -2509,7 +2733,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -2524,7 +2748,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -2544,7 +2768,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -2562,16 +2786,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -2580,7 +2804,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2589,4 +2813,272 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="ポイント履歴" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="243">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -392,6 +393,30 @@
     <t>カスタム項目、付与ポイント合計－利用ポイント合計</t>
   </si>
   <si>
+    <t>FavoriteBeans__c</t>
+  </si>
+  <si>
+    <t>好みの豆・挽き方</t>
+  </si>
+  <si>
+    <t>好みの豆・挽き方（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、どの店舗でも同じ接客ができるように記録</t>
+  </si>
+  <si>
+    <t>ServiceNote__c</t>
+  </si>
+  <si>
+    <t>接客メモ</t>
+  </si>
+  <si>
+    <t>接客メモ（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、来店頻度・苦手な味など</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -639,6 +664,90 @@
   </si>
   <si>
     <t>初期値：今日</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ケースオブジェクト（Case）</t>
+  </si>
+  <si>
+    <t>CaseNumber</t>
+  </si>
+  <si>
+    <t>ケース番号</t>
+  </si>
+  <si>
+    <t>問い合わせ番号</t>
+  </si>
+  <si>
+    <t>Salesforce標準</t>
+  </si>
+  <si>
+    <t>取引先責任者</t>
+  </si>
+  <si>
+    <t>参照（Contact）</t>
+  </si>
+  <si>
+    <t>問い合わせしたお客様</t>
+  </si>
+  <si>
+    <t>お客様の取引先から設定</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>発生源</t>
+  </si>
+  <si>
+    <t>受付方法</t>
+  </si>
+  <si>
+    <t>電話/メール/Web</t>
+  </si>
+  <si>
+    <t>状況</t>
+  </si>
+  <si>
+    <t>対応状況</t>
+  </si>
+  <si>
+    <t>新規/対応中/エスカレーション/クローズ</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>件名</t>
+  </si>
+  <si>
+    <t>問い合わせ内容</t>
+  </si>
+  <si>
+    <t>受付店舗</t>
+  </si>
+  <si>
+    <t>受付店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、グローバル値セット「店舗」を利用</t>
+  </si>
+  <si>
+    <t>InquiryCategory__c</t>
+  </si>
+  <si>
+    <t>問い合わせ区分</t>
+  </si>
+  <si>
+    <t>問い合わせ区分（カスタム）</t>
+  </si>
+  <si>
+    <t>豆・商品について/ギフト/定期便/配送/ポイント/法人のお取引/その他</t>
+  </si>
+  <si>
+    <t>ケース所有者</t>
+  </si>
+  <si>
+    <t>対応担当者</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2064,6 +2173,56 @@
       </c>
       <c r="I18" s="23" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="21">
+        <v>255</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="21">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="22"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2249,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2143,10 +2302,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2171,10 +2330,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2190,7 +2349,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2218,13 +2377,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2234,24 +2393,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2268,13 +2427,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2289,16 +2448,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
@@ -2307,18 +2466,18 @@
         <v>113</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2326,7 +2485,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2341,7 +2500,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2361,7 +2520,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2379,13 +2538,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2404,13 +2563,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2418,13 +2577,13 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2451,7 +2610,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2504,10 +2663,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2577,13 +2736,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2671,13 +2830,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2687,7 +2846,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -2696,13 +2855,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -2710,7 +2869,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -2719,13 +2878,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -2733,7 +2892,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -2748,7 +2907,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -2768,7 +2927,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -2786,16 +2945,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -2804,7 +2963,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2831,7 +2990,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2842,7 +3001,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2884,10 +3043,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2912,10 +3071,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>82</v>
@@ -2927,21 +3086,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -2952,18 +3111,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -2971,24 +3130,24 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -2996,24 +3155,24 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
@@ -3025,18 +3184,18 @@
         <v>9</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3048,12 +3207,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3071,8 +3230,322 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>206</v>
-      </c>
+        <v>214</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4">
+        <v>255</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="4">
+        <v>32000</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -11,7 +11,7 @@
     <sheet sheetId="2" name="取引先責任者" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="ポイント履歴" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="購入・ポイント履歴" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="261">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -417,6 +417,30 @@
     <t>カスタム項目、来店頻度・苦手な味など</t>
   </si>
   <si>
+    <t>LastVisitDate__c</t>
+  </si>
+  <si>
+    <t>最終来店日</t>
+  </si>
+  <si>
+    <t>最終来店日（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、購入・ポイント履歴（区分＝付与）の日付の最大値</t>
+  </si>
+  <si>
+    <t>PurchaseCount__c</t>
+  </si>
+  <si>
+    <t>購入回数</t>
+  </si>
+  <si>
+    <t>購入回数（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、購入・ポイント履歴（区分＝付与）の件数</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -591,7 +615,7 @@
     <t>商談化時に自動でTrue</t>
   </si>
   <si>
-    <t>項目定義書　－ ポイント履歴オブジェクト（PointHistory__c）</t>
+    <t>項目定義書　－ 購入・ポイント履歴オブジェクト（PointHistory__c）</t>
   </si>
   <si>
     <t>Id</t>
@@ -600,7 +624,7 @@
     <t>ポイント履歴ID</t>
   </si>
   <si>
-    <t>ポイント履歴番号</t>
+    <t>履歴番号</t>
   </si>
   <si>
     <t>PH-00000形式</t>
@@ -664,6 +688,36 @@
   </si>
   <si>
     <t>初期値：今日</t>
+  </si>
+  <si>
+    <t>Product__c</t>
+  </si>
+  <si>
+    <t>商品</t>
+  </si>
+  <si>
+    <t>参照（Product2）</t>
+  </si>
+  <si>
+    <t>商品マスタ（標準の商品オブジェクト）を参照</t>
+  </si>
+  <si>
+    <t>Size__c</t>
+  </si>
+  <si>
+    <t>内容量</t>
+  </si>
+  <si>
+    <t>100g/200g/500g/ギフト</t>
+  </si>
+  <si>
+    <t>Quantity__c</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>初期値：1</t>
   </si>
   <si>
     <t>項目定義書　－ ケースオブジェクト（Case）</t>
@@ -1761,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2223,6 +2277,52 @@
       </c>
       <c r="I20" s="23" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2249,7 +2349,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2260,7 +2360,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2302,10 +2402,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2330,10 +2430,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2349,7 +2449,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2377,13 +2477,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2393,24 +2493,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2427,13 +2527,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2448,16 +2548,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
@@ -2466,18 +2566,18 @@
         <v>113</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2485,7 +2585,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2500,7 +2600,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2520,7 +2620,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2538,13 +2638,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2563,13 +2663,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2577,13 +2677,13 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2610,7 +2710,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2663,10 +2763,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2736,13 +2836,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2830,13 +2930,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2846,7 +2946,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -2855,13 +2955,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -2869,7 +2969,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -2878,13 +2978,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -2892,7 +2992,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -2907,7 +3007,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -2927,7 +3027,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -2945,16 +3045,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -2963,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3076,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2990,7 +3090,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3043,10 +3143,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3071,10 +3171,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>82</v>
@@ -3086,21 +3186,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -3111,18 +3211,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3130,24 +3230,24 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3155,24 +3255,24 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
@@ -3184,18 +3284,18 @@
         <v>9</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3207,12 +3307,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3230,7 +3330,76 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3258,7 +3427,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3269,7 +3438,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3311,13 +3480,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>82</v>
@@ -3329,7 +3498,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3337,13 +3506,13 @@
         <v>80</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -3352,7 +3521,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3375,18 +3544,18 @@
         <v>113</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3394,7 +3563,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
@@ -3405,13 +3574,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3421,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
@@ -3432,13 +3601,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -3461,7 +3630,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -3478,13 +3647,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -3492,24 +3661,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
@@ -3517,7 +3686,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -3531,10 +3700,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>59</v>
@@ -3552,6 +3721,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -13,13 +13,14 @@
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="購入・ポイント履歴" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="クーポン" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="293">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -802,6 +803,102 @@
   </si>
   <si>
     <t>対応担当者</t>
+  </si>
+  <si>
+    <t>項目定義書　－ クーポンオブジェクト（Coupon__c）</t>
+  </si>
+  <si>
+    <t>クーポンID</t>
+  </si>
+  <si>
+    <t>クーポン番号</t>
+  </si>
+  <si>
+    <t>CP-00000形式</t>
+  </si>
+  <si>
+    <t>Content__c</t>
+  </si>
+  <si>
+    <t>クーポン内容</t>
+  </si>
+  <si>
+    <t>例：200g 1袋 300円引き</t>
+  </si>
+  <si>
+    <t>IssueDate__c</t>
+  </si>
+  <si>
+    <t>発行日</t>
+  </si>
+  <si>
+    <t>ExpirationDate__c</t>
+  </si>
+  <si>
+    <t>有効期限</t>
+  </si>
+  <si>
+    <t>数式（日付）</t>
+  </si>
+  <si>
+    <t>発行日＋30日</t>
+  </si>
+  <si>
+    <t>IssuedStore__c</t>
+  </si>
+  <si>
+    <t>発行店舗</t>
+  </si>
+  <si>
+    <t>NotificationMethod__c</t>
+  </si>
+  <si>
+    <t>発行の連絡方法</t>
+  </si>
+  <si>
+    <t>メール/店頭で手渡し/郵送</t>
+  </si>
+  <si>
+    <t>発行したことの連絡履歴</t>
+  </si>
+  <si>
+    <t>NotifiedDate__c</t>
+  </si>
+  <si>
+    <t>連絡日</t>
+  </si>
+  <si>
+    <t>UsedDate__c</t>
+  </si>
+  <si>
+    <t>使用日</t>
+  </si>
+  <si>
+    <t>入力規則：1回限り（一度入れたら変更不可）、有効期限後は入力不可</t>
+  </si>
+  <si>
+    <t>UsedStore__c</t>
+  </si>
+  <si>
+    <t>使用店舗</t>
+  </si>
+  <si>
+    <t>入力規則：使用日を入れたら必須</t>
+  </si>
+  <si>
+    <t>Status__c</t>
+  </si>
+  <si>
+    <t>状態</t>
+  </si>
+  <si>
+    <t>数式（テキスト）</t>
+  </si>
+  <si>
+    <t>利用可能/使用済み/期限切れ</t>
+  </si>
+  <si>
+    <t>使用日と有効期限から自動判定</t>
   </si>
 </sst>
 </file>
@@ -2360,7 +2457,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3723,4 +3820,370 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4">
+        <v>100</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="314">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -259,6 +259,21 @@
     <t>カスタム項目、Issue #1 の手順練習用</t>
   </si>
   <si>
+    <t>ResponsibleStore__c</t>
+  </si>
+  <si>
+    <t>法人担当店舗</t>
+  </si>
+  <si>
+    <t>法人担当店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ</t>
+  </si>
+  <si>
+    <t>カスタム項目、この会社への営業を担当する店舗</t>
+  </si>
+  <si>
     <t>項目定義書　－ 取引先責任者オブジェクト（Contact）</t>
   </si>
   <si>
@@ -550,6 +565,63 @@
     <t>カスタム項目、失注時は必須</t>
   </si>
   <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>営業した店舗</t>
+  </si>
+  <si>
+    <t>営業した店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>DealType__c</t>
+  </si>
+  <si>
+    <t>取引種別</t>
+  </si>
+  <si>
+    <t>取引種別（カスタム）</t>
+  </si>
+  <si>
+    <t>オフィス向け定期便/業務用卸</t>
+  </si>
+  <si>
+    <t>SalesRep__c</t>
+  </si>
+  <si>
+    <t>店舗の営業担当者</t>
+  </si>
+  <si>
+    <t>店舗の営業担当者（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、店舗スタッフの名前</t>
+  </si>
+  <si>
+    <t>LastContactDate__c</t>
+  </si>
+  <si>
+    <t>最終連絡日</t>
+  </si>
+  <si>
+    <t>最終連絡日（カスタム）</t>
+  </si>
+  <si>
+    <t>OtherStoreAlert__c</t>
+  </si>
+  <si>
+    <t>担当店舗の確認</t>
+  </si>
+  <si>
+    <t>担当店舗の確認（カスタム）</t>
+  </si>
+  <si>
+    <t>数式（テキスト）</t>
+  </si>
+  <si>
+    <t>カスタム項目、営業した店舗が取引先の法人担当店舗と違うときに警告を表示</t>
+  </si>
+  <si>
     <t>項目定義書　－ リードオブジェクト（Lead）</t>
   </si>
   <si>
@@ -643,15 +715,9 @@
     <t>取引先責任者への主従関係</t>
   </si>
   <si>
-    <t>Store__c</t>
-  </si>
-  <si>
     <t>店舗</t>
   </si>
   <si>
-    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ</t>
-  </si>
-  <si>
     <t>グローバル値セット「店舗」を利用</t>
   </si>
   <si>
@@ -890,9 +956,6 @@
   </si>
   <si>
     <t>状態</t>
-  </si>
-  <si>
-    <t>数式（テキスト）</t>
   </si>
   <si>
     <t>利用可能/使用済み/期限切れ</t>
@@ -1478,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1900,6 +1963,31 @@
       </c>
       <c r="I18" s="19" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1926,7 +2014,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1979,10 +2067,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -1999,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2007,13 +2095,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
@@ -2024,18 +2112,18 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -2054,13 +2142,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2077,13 +2165,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -2100,13 +2188,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -2123,16 +2211,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E10" s="10">
         <v>80</v>
@@ -2152,7 +2240,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>50</v>
@@ -2169,13 +2257,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>50</v>
@@ -2192,13 +2280,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>45</v>
@@ -2216,7 +2304,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>58</v>
@@ -2234,13 +2322,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>20</v>
@@ -2254,87 +2342,87 @@
         <v>25</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22"/>
       <c r="G16" s="21"/>
       <c r="H16" s="21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>117</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>112</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="22"/>
       <c r="G17" s="21"/>
       <c r="H17" s="21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="22"/>
       <c r="G18" s="21"/>
       <c r="H18" s="21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>20</v>
@@ -2348,18 +2436,18 @@
         <v>25</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>64</v>
@@ -2373,53 +2461,53 @@
         <v>25</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="22"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="22"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2432,7 +2520,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2446,7 +2534,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2457,7 +2545,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2499,10 +2587,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2519,7 +2607,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2527,10 +2615,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2546,7 +2634,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2557,10 +2645,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="20" t="s">
@@ -2574,13 +2662,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2590,24 +2678,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2624,13 +2712,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2645,36 +2733,36 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2682,7 +2770,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2697,7 +2785,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2717,7 +2805,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2735,13 +2823,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2760,13 +2848,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2774,13 +2862,134 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>175</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="17">
+        <v>40</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2807,7 +3016,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2860,10 +3069,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2880,18 +3089,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2910,13 +3119,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -2933,13 +3142,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2958,13 +3167,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -2981,16 +3190,16 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E9" s="7">
         <v>80</v>
@@ -3027,13 +3236,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -3043,7 +3252,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -3052,13 +3261,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -3066,7 +3275,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -3075,13 +3284,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -3089,7 +3298,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3104,7 +3313,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -3124,7 +3333,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -3142,16 +3351,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -3160,7 +3369,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3187,7 +3396,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3240,10 +3449,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3260,7 +3469,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3268,13 +3477,13 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -3283,21 +3492,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -3308,18 +3517,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3327,24 +3536,24 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3352,24 +3561,24 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
@@ -3381,18 +3590,18 @@
         <v>9</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3404,12 +3613,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3427,21 +3636,21 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
@@ -3450,18 +3659,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
@@ -3469,7 +3678,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
@@ -3478,13 +3687,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>42</v>
@@ -3496,7 +3705,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3733,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3577,16 +3786,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5"/>
@@ -3595,21 +3804,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -3618,7 +3827,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3626,33 +3835,33 @@
         <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3660,7 +3869,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
@@ -3671,13 +3880,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3687,7 +3896,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
@@ -3698,13 +3907,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -3727,7 +3936,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -3744,13 +3953,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -3758,24 +3967,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
@@ -3783,7 +3992,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -3797,10 +4006,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>59</v>
@@ -3838,7 +4047,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3849,7 +4058,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3891,10 +4100,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3911,7 +4120,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3919,13 +4128,13 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -3934,21 +4143,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -3959,18 +4168,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
@@ -3984,18 +4193,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
@@ -4009,41 +4218,41 @@
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
@@ -4051,24 +4260,24 @@
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
       <c r="G10" s="4" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4076,24 +4285,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>73</v>
@@ -4108,13 +4317,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>73</v>
@@ -4126,18 +4335,18 @@
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
@@ -4145,38 +4354,38 @@
       <c r="E14" s="4"/>
       <c r="F14" s="5"/>
       <c r="G14" s="4" t="s">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4184,6 +4393,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -14,13 +14,14 @@
     <sheet sheetId="5" name="購入・ポイント履歴" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="クーポン" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="キャンペーンメンバー" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="331">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -962,6 +963,57 @@
   </si>
   <si>
     <t>使用日と有効期限から自動判定</t>
+  </si>
+  <si>
+    <t>項目定義書　－ キャンペーンメンバーオブジェクト（CampaignMember）</t>
+  </si>
+  <si>
+    <t>CampaignId</t>
+  </si>
+  <si>
+    <t>キャンペーン</t>
+  </si>
+  <si>
+    <t>参照（Campaign）</t>
+  </si>
+  <si>
+    <t>1人のお客様は同じキャンペーンに1回だけ登録できる（重複案内の防止）</t>
+  </si>
+  <si>
+    <t>送信済み/反応あり</t>
+  </si>
+  <si>
+    <t>HasResponded</t>
+  </si>
+  <si>
+    <t>反応あり</t>
+  </si>
+  <si>
+    <t>状況から自動設定</t>
+  </si>
+  <si>
+    <t>SentChannel__c</t>
+  </si>
+  <si>
+    <t>案内方法</t>
+  </si>
+  <si>
+    <t>案内方法（カスタム）</t>
+  </si>
+  <si>
+    <t>メール/店頭で声かけ/はがき</t>
+  </si>
+  <si>
+    <t>ResponseStore__c</t>
+  </si>
+  <si>
+    <t>反応した店舗</t>
+  </si>
+  <si>
+    <t>反応した店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、店舗横断で効果を比べるため</t>
   </si>
 </sst>
 </file>
@@ -2545,7 +2597,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4395,4 +4447,224 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="348">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -458,6 +458,60 @@
     <t>カスタム項目、購入・ポイント履歴（区分＝付与）の件数</t>
   </si>
   <si>
+    <t>PreviousVisitCount__c</t>
+  </si>
+  <si>
+    <t>移行前の来店回数</t>
+  </si>
+  <si>
+    <t>移行前の来店回数（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、導入前の台帳・スタンプカードの来店回数</t>
+  </si>
+  <si>
+    <t>TotalVisitCount__c</t>
+  </si>
+  <si>
+    <t>累計来店回数</t>
+  </si>
+  <si>
+    <t>累計来店回数（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、移行前の来店回数＋購入回数</t>
+  </si>
+  <si>
+    <t>DaysSinceLastVisit__c</t>
+  </si>
+  <si>
+    <t>最終来店からの日数</t>
+  </si>
+  <si>
+    <t>最終来店からの日数（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、今日－最終来店日</t>
+  </si>
+  <si>
+    <t>CustomerRank__c</t>
+  </si>
+  <si>
+    <t>お客様ランク</t>
+  </si>
+  <si>
+    <t>お客様ランク（カスタム）</t>
+  </si>
+  <si>
+    <t>数式（テキスト）</t>
+  </si>
+  <si>
+    <t>★常連/一般/休眠（60日以上来店なし）/新規（購入履歴なし）</t>
+  </si>
+  <si>
+    <t>カスタム項目、常連＝累計来店5回以上かつ60日以内に来店。画面上部に表示</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -615,9 +669,6 @@
   </si>
   <si>
     <t>担当店舗の確認（カスタム）</t>
-  </si>
-  <si>
-    <t>数式（テキスト）</t>
   </si>
   <si>
     <t>カスタム項目、営業した店舗が取引先の法人担当店舗と違うときに警告を表示</t>
@@ -2052,7 +2103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2560,6 +2611,100 @@
       </c>
       <c r="I22" s="23" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="23" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2586,7 +2731,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2597,7 +2742,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2639,10 +2784,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2667,10 +2812,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2686,7 +2831,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2714,13 +2859,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2730,24 +2875,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2764,13 +2909,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2785,16 +2930,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
@@ -2803,18 +2948,18 @@
         <v>118</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2822,7 +2967,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2837,7 +2982,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2857,7 +3002,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2875,13 +3020,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2900,13 +3045,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2914,24 +3059,24 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>29</v>
@@ -2950,13 +3095,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>29</v>
@@ -2964,7 +3109,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="17" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>25</v>
@@ -2975,13 +3120,13 @@
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>20</v>
@@ -2995,18 +3140,18 @@
         <v>25</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>73</v>
@@ -3023,16 +3168,16 @@
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
@@ -3041,7 +3186,7 @@
         <v>118</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -3068,7 +3213,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3121,10 +3266,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3194,13 +3339,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -3288,13 +3433,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -3304,7 +3449,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -3313,13 +3458,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -3327,7 +3472,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -3336,13 +3481,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -3350,7 +3495,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3365,7 +3510,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -3385,7 +3530,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -3403,16 +3548,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -3421,7 +3566,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3448,7 +3593,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3501,10 +3646,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3529,10 +3674,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -3544,21 +3689,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -3569,18 +3714,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3594,18 +3739,18 @@
         <v>9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3613,24 +3758,24 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
@@ -3642,18 +3787,18 @@
         <v>9</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3665,12 +3810,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3688,21 +3833,21 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
@@ -3711,18 +3856,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
@@ -3730,7 +3875,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
@@ -3739,13 +3884,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>42</v>
@@ -3757,7 +3902,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +3930,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3838,13 +3983,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>87</v>
@@ -3856,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3864,13 +4009,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -3879,7 +4024,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3902,18 +4047,18 @@
         <v>118</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3921,7 +4066,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
@@ -3932,13 +4077,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3948,7 +4093,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
@@ -3959,13 +4104,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -3988,7 +4133,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -4005,13 +4150,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4025,18 +4170,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
@@ -4044,7 +4189,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -4058,10 +4203,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>59</v>
@@ -4099,7 +4244,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4152,10 +4297,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4180,10 +4325,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -4195,21 +4340,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -4220,18 +4365,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
@@ -4245,18 +4390,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
@@ -4270,21 +4415,21 @@
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
@@ -4293,18 +4438,18 @@
         <v>118</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
@@ -4318,18 +4463,18 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4337,24 +4482,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>73</v>
@@ -4369,13 +4514,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>73</v>
@@ -4387,18 +4532,18 @@
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
@@ -4409,35 +4554,35 @@
         <v>82</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>118</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4465,7 +4610,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4476,7 +4621,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4518,16 +4663,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5" t="s">
@@ -4538,7 +4683,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4546,13 +4691,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4564,13 +4709,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
@@ -4578,7 +4723,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>9</v>
@@ -4589,16 +4734,16 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
@@ -4607,18 +4752,18 @@
         <v>118</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4626,7 +4771,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>25</v>
@@ -4637,13 +4782,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
@@ -4657,7 +4802,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -4665,6 +4810,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="349">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -791,7 +791,10 @@
     <t>ポイント数</t>
   </si>
   <si>
-    <t>正の整数で入力</t>
+    <t>自動/必須</t>
+  </si>
+  <si>
+    <t>付与：購入金額100円で1ポイントを自動計算（フロー「購入ポイント自動計算」）／利用：使ったポイント数を入力</t>
   </si>
   <si>
     <t>PurchaseAmount__c</t>
@@ -3784,21 +3787,21 @@
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>9</v>
+        <v>256</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3810,12 +3813,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3833,21 +3836,21 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
@@ -3856,18 +3859,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
@@ -3875,7 +3878,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
@@ -3884,13 +3887,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>42</v>
@@ -3902,7 +3905,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -3930,7 +3933,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3983,13 +3986,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>87</v>
@@ -4001,7 +4004,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4009,13 +4012,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4024,7 +4027,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4047,18 +4050,18 @@
         <v>118</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -4066,7 +4069,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
@@ -4080,10 +4083,10 @@
         <v>222</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4093,7 +4096,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
@@ -4104,13 +4107,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -4133,7 +4136,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -4153,10 +4156,10 @@
         <v>199</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4170,18 +4173,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
@@ -4189,7 +4192,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -4203,10 +4206,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>59</v>
@@ -4244,7 +4247,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4300,7 +4303,7 @@
         <v>240</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4325,10 +4328,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -4340,7 +4343,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4370,13 +4373,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
@@ -4390,18 +4393,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
@@ -4415,21 +4418,21 @@
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
@@ -4438,18 +4441,18 @@
         <v>118</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
@@ -4468,13 +4471,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4482,24 +4485,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>73</v>
@@ -4514,13 +4517,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>73</v>
@@ -4532,18 +4535,18 @@
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
@@ -4557,18 +4560,18 @@
         <v>197</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>160</v>
@@ -4576,13 +4579,13 @@
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>118</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4610,7 +4613,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4663,16 +4666,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5" t="s">
@@ -4683,7 +4686,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4691,13 +4694,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4712,10 +4715,10 @@
         <v>222</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
@@ -4723,7 +4726,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>9</v>
@@ -4734,13 +4737,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>237</v>
@@ -4752,18 +4755,18 @@
         <v>118</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4771,7 +4774,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>25</v>
@@ -4782,13 +4785,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
@@ -4802,7 +4805,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="353">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -512,6 +512,18 @@
     <t>カスタム項目、常連＝累計来店5回以上かつ60日以内に来店。画面上部に表示</t>
   </si>
   <si>
+    <t>LastWinbackCouponDate__c</t>
+  </si>
+  <si>
+    <t>休眠クーポン発行日</t>
+  </si>
+  <si>
+    <t>休眠クーポン発行日（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、60日以上来店のないお客様へ10%オフクーポンを自動発行した日（毎朝6時に実行）</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -944,7 +956,7 @@
     <t>クーポン内容</t>
   </si>
   <si>
-    <t>例：200g 1袋 300円引き</t>
+    <t>例：200g 1袋 300円引き。自動発行分は「次回お会計時10%オフ（60日以上ご来店のないお客様へ）」</t>
   </si>
   <si>
     <t>IssueDate__c</t>
@@ -2106,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2708,6 +2720,29 @@
       </c>
       <c r="I26" s="23" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2734,7 +2769,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2787,10 +2822,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2815,10 +2850,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2834,7 +2869,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2862,13 +2897,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2878,24 +2913,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2912,13 +2947,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2933,16 +2968,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
@@ -2951,18 +2986,18 @@
         <v>118</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2970,7 +3005,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2985,7 +3020,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -3005,7 +3040,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -3023,13 +3058,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -3048,13 +3083,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -3062,24 +3097,24 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>29</v>
@@ -3098,13 +3133,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>29</v>
@@ -3112,7 +3147,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="17" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>25</v>
@@ -3123,13 +3158,13 @@
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>20</v>
@@ -3143,18 +3178,18 @@
         <v>25</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>73</v>
@@ -3171,13 +3206,13 @@
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>160</v>
@@ -3189,7 +3224,7 @@
         <v>118</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -3216,7 +3251,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3269,10 +3304,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3342,13 +3377,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -3436,13 +3471,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -3452,7 +3487,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -3461,13 +3496,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -3475,7 +3510,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -3484,13 +3519,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -3498,7 +3533,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3513,7 +3548,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -3533,7 +3568,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -3551,16 +3586,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -3569,7 +3604,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3631,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3649,10 +3684,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3677,10 +3712,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -3692,21 +3727,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -3717,18 +3752,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3742,18 +3777,18 @@
         <v>9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3761,24 +3796,24 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
@@ -3787,21 +3822,21 @@
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3813,12 +3848,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3836,21 +3871,21 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
@@ -3859,18 +3894,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
@@ -3878,7 +3913,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
@@ -3887,13 +3922,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>42</v>
@@ -3905,7 +3940,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3933,7 +3968,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3986,13 +4021,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>87</v>
@@ -4004,7 +4039,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4012,13 +4047,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4027,7 +4062,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4050,18 +4085,18 @@
         <v>118</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -4069,7 +4104,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
@@ -4080,13 +4115,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4096,7 +4131,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
@@ -4107,13 +4142,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -4136,7 +4171,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -4153,13 +4188,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4173,18 +4208,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
@@ -4192,7 +4227,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -4206,10 +4241,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>59</v>
@@ -4247,7 +4282,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4300,10 +4335,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4328,10 +4363,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -4343,21 +4378,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -4368,18 +4403,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
@@ -4393,18 +4428,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
@@ -4418,21 +4453,21 @@
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
@@ -4441,18 +4476,18 @@
         <v>118</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
@@ -4466,18 +4501,18 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4485,24 +4520,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>73</v>
@@ -4517,13 +4552,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>73</v>
@@ -4535,18 +4570,18 @@
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
@@ -4557,21 +4592,21 @@
         <v>82</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>160</v>
@@ -4579,13 +4614,13 @@
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>118</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4613,7 +4648,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4666,16 +4701,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5" t="s">
@@ -4686,7 +4721,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4694,13 +4729,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4712,13 +4747,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
@@ -4726,7 +4761,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>9</v>
@@ -4737,16 +4772,16 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
@@ -4755,18 +4790,18 @@
         <v>118</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4774,7 +4809,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>25</v>
@@ -4785,13 +4820,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
@@ -4805,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="361">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -524,6 +524,33 @@
     <t>カスタム項目、60日以上来店のないお客様へ10%オフクーポンを自動発行した日（毎朝6時に実行）</t>
   </si>
   <si>
+    <t>OnlineSubscription__c</t>
+  </si>
+  <si>
+    <t>オンライン定期便 利用中</t>
+  </si>
+  <si>
+    <t>オンライン定期便 利用中（カスタム）</t>
+  </si>
+  <si>
+    <t>チェックボックス</t>
+  </si>
+  <si>
+    <t>カスタム項目、個人向けオンライン定期便の利用者</t>
+  </si>
+  <si>
+    <t>SubscriptionNote__c</t>
+  </si>
+  <si>
+    <t>定期便の内容</t>
+  </si>
+  <si>
+    <t>定期便の内容（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、届けている豆など</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -744,9 +771,6 @@
   </si>
   <si>
     <t>商談化フラグ</t>
-  </si>
-  <si>
-    <t>チェックボックス</t>
   </si>
   <si>
     <t>商談化時に自動でTrue</t>
@@ -2118,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2743,6 +2767,54 @@
       </c>
       <c r="I27" s="23" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="28" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="21">
+        <v>255</v>
+      </c>
+      <c r="F29" s="22"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2769,7 +2841,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2822,10 +2894,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2850,10 +2922,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2869,7 +2941,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2897,13 +2969,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2913,24 +2985,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2947,13 +3019,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2968,16 +3040,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
@@ -2986,18 +3058,18 @@
         <v>118</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -3005,7 +3077,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -3020,7 +3092,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -3040,7 +3112,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -3058,13 +3130,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -3083,13 +3155,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -3097,24 +3169,24 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>29</v>
@@ -3133,13 +3205,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>29</v>
@@ -3147,7 +3219,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="18"/>
       <c r="G17" s="17" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>25</v>
@@ -3158,13 +3230,13 @@
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>20</v>
@@ -3178,18 +3250,18 @@
         <v>25</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>73</v>
@@ -3206,13 +3278,13 @@
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>160</v>
@@ -3224,7 +3296,7 @@
         <v>118</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -3251,7 +3323,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3304,10 +3376,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3377,13 +3449,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -3471,13 +3543,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -3487,7 +3559,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -3496,13 +3568,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -3510,7 +3582,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -3519,13 +3591,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -3533,7 +3605,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3548,7 +3620,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -3568,7 +3640,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -3586,16 +3658,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -3604,7 +3676,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3631,7 +3703,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3684,10 +3756,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3712,10 +3784,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -3727,21 +3799,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -3752,18 +3824,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -3777,18 +3849,18 @@
         <v>9</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -3796,24 +3868,24 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
@@ -3822,21 +3894,21 @@
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>38</v>
@@ -3848,12 +3920,12 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>73</v>
@@ -3871,21 +3943,21 @@
         <v>9</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
@@ -3894,18 +3966,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
@@ -3913,7 +3985,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
@@ -3922,13 +3994,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>42</v>
@@ -3940,7 +4012,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +4040,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4021,13 +4093,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>87</v>
@@ -4039,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4047,13 +4119,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4062,7 +4134,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4085,18 +4157,18 @@
         <v>118</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -4104,7 +4176,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>25</v>
@@ -4115,13 +4187,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4131,7 +4203,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
@@ -4142,13 +4214,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -4171,7 +4243,7 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -4188,13 +4260,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4208,18 +4280,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
@@ -4227,7 +4299,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -4241,10 +4313,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>59</v>
@@ -4282,7 +4354,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4335,10 +4407,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4363,10 +4435,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>87</v>
@@ -4378,21 +4450,21 @@
         <v>16</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="5" t="s">
@@ -4403,18 +4475,18 @@
         <v>9</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
@@ -4428,18 +4500,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
@@ -4453,21 +4525,21 @@
         <v>9</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
@@ -4476,18 +4548,18 @@
         <v>118</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
@@ -4501,18 +4573,18 @@
         <v>25</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
@@ -4520,24 +4592,24 @@
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>73</v>
@@ -4552,13 +4624,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>73</v>
@@ -4570,18 +4642,18 @@
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
@@ -4592,21 +4664,21 @@
         <v>82</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>160</v>
@@ -4614,13 +4686,13 @@
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>118</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4648,7 +4720,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4701,16 +4773,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5" t="s">
@@ -4721,7 +4793,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4729,13 +4801,13 @@
         <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -4747,13 +4819,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>29</v>
@@ -4761,7 +4833,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>9</v>
@@ -4772,16 +4844,16 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
@@ -4790,18 +4862,18 @@
         <v>118</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
@@ -4809,7 +4881,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>25</v>
@@ -4820,13 +4892,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
@@ -4840,7 +4912,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -509,7 +509,7 @@
     <t>★常連/一般/休眠（60日以上来店なし）/新規（購入履歴なし）</t>
   </si>
   <si>
-    <t>カスタム項目、常連＝累計来店5回以上かつ60日以内に来店。画面上部に表示</t>
+    <t>カスタム項目、常連＝累計来店5回以上かつ60日以内に来店。電話番号の横（画面上部・詳細欄）に表示</t>
   </si>
   <si>
     <t>LastWinbackCouponDate__c</t>
